--- a/Pricing Logic/modules/manual/output_703_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_703_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="19">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,40 +37,40 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>حبوبة خل- 900 مل</t>
-  </si>
-  <si>
-    <t>زيت قلية خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>صابون جوى عرض خاص  - 165 جم</t>
-  </si>
-  <si>
-    <t>اندومى خضار سوبر مى عرض 44 كيس - 70 جم</t>
-  </si>
-  <si>
-    <t>حفاضات بى بم بانتس جامبو مقاس 4 - 56 حفاضة</t>
-  </si>
-  <si>
-    <t>زيت عافية ذرة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>ويفر تاوتاو كليك كاكاو - 5 جنية</t>
-  </si>
-  <si>
-    <t>مولفكس بريميوم جامبو اقتصادي مقاس 2 ميني- 58 حفاضة</t>
-  </si>
-  <si>
-    <t>اندومي سوبر مى خضار حارجامبو عرض 44 كيس - 100 جم</t>
-  </si>
-  <si>
-    <t>بسكويت شاي شوجر زبدة- 5 جنية</t>
+    <t>مكرونة حواء فرن - 400 جم</t>
+  </si>
+  <si>
+    <t>مكرونة حواء شعرية - 400 جم</t>
+  </si>
+  <si>
+    <t>لبن بخيره - 500 مل</t>
+  </si>
+  <si>
+    <t>لبن بخيره - 1 لتر</t>
+  </si>
+  <si>
+    <t>بيبسى تربو - 390 مل</t>
+  </si>
+  <si>
+    <t>تونة دولفين مفتتة بارد 170 جم + 30 جم - 200 جم</t>
+  </si>
+  <si>
+    <t>مناديل بابيا تواليت 3 طبقات 5 رول + 1 رول هدية - 6 رول</t>
+  </si>
+  <si>
+    <t>بن عبد المعبود محوج وسط - 100 جم</t>
+  </si>
+  <si>
+    <t>مسحوق ليدر عادى لافندر - 2 كجم</t>
+  </si>
+  <si>
+    <t>ميرندا برتقال هضبه - 250 مل</t>
   </si>
   <si>
     <t>YES</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -456,7 +456,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -465,15 +465,15 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>146</v>
+        <v>265</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>470</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -482,75 +482,75 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>831</v>
+        <v>265</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>2188</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>493</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>2188</v>
+        <v>151</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>2193</v>
+        <v>593</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>262.25</v>
+        <v>127.5</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>2419</v>
+        <v>3430</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>271.5</v>
+        <v>405</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -558,172 +558,138 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>2419</v>
+        <v>3430</v>
       </c>
       <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
         <v>11</v>
       </c>
-      <c r="C8">
-        <v>29</v>
-      </c>
       <c r="D8">
-        <v>814.5</v>
+        <v>33.75</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>2538</v>
+        <v>3430</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>964.25</v>
+        <v>810</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>12924</v>
+        <v>3430</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>565</v>
+        <v>1620</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>13036</v>
+        <v>4032</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D11">
-        <v>609</v>
+        <v>315</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>13036</v>
+        <v>4223</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>50.75</v>
+        <v>734.5</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19965</v>
+        <v>4223</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>260.25</v>
+        <v>8814</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19965</v>
+        <v>10124</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>780.75</v>
+        <v>290.75</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20927</v>
+        <v>25960</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>365</v>
+        <v>107.25</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>25289</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>188</v>
-      </c>
-      <c r="E16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>25289</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17">
-        <v>3</v>
-      </c>
-      <c r="D17">
-        <v>23.5</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/manual/output_703_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_703_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,40 +37,34 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>مكرونة حواء فرن - 400 جم</t>
-  </si>
-  <si>
-    <t>مكرونة حواء شعرية - 400 جم</t>
-  </si>
-  <si>
-    <t>لبن بخيره - 500 مل</t>
-  </si>
-  <si>
-    <t>لبن بخيره - 1 لتر</t>
-  </si>
-  <si>
-    <t>بيبسى تربو - 390 مل</t>
-  </si>
-  <si>
-    <t>تونة دولفين مفتتة بارد 170 جم + 30 جم - 200 جم</t>
-  </si>
-  <si>
-    <t>مناديل بابيا تواليت 3 طبقات 5 رول + 1 رول هدية - 6 رول</t>
-  </si>
-  <si>
-    <t>بن عبد المعبود محوج وسط - 100 جم</t>
-  </si>
-  <si>
-    <t>مسحوق ليدر عادى لافندر - 2 كجم</t>
-  </si>
-  <si>
-    <t>ميرندا برتقال هضبه - 250 مل</t>
+    <t>راني عصير خوخ حبيبات- 235 مل</t>
+  </si>
+  <si>
+    <t>زيت عافية ذرة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>سوفى ماكسى بالمسك طويل سميكة عرض خاص - 16 فوطة</t>
+  </si>
+  <si>
+    <t>سبرايت - 0.95 لتر</t>
+  </si>
+  <si>
+    <t>لبان تشكلتس نعناع - 0.5 جنية</t>
+  </si>
+  <si>
+    <t>لبان تشكلتس فراولة - 0.5 جنية</t>
+  </si>
+  <si>
+    <t>حفاضات جود كير مقاس 5 - 100 حفاضة</t>
+  </si>
+  <si>
+    <t>زيت عافية ذرة - 700 مل</t>
+  </si>
+  <si>
+    <t>باندا مثلثات - 8 قطعه</t>
   </si>
   <si>
     <t>YES</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -456,24 +450,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>35</v>
+        <v>202</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>265</v>
+        <v>402.5</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>39</v>
+        <v>2538</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -482,15 +476,15 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>265</v>
+        <v>920</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>130</v>
+        <v>2912</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -499,100 +493,100 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>493</v>
+        <v>606</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>151</v>
+        <v>2912</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>441</v>
+        <v>75.75</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>593</v>
+        <v>3674</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>127.5</v>
+        <v>123.75</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>3430</v>
+        <v>5208</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>405</v>
+        <v>1605</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>3430</v>
+        <v>5208</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>33.75</v>
+        <v>53.5</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>3430</v>
+        <v>5209</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>810</v>
+        <v>51.75</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>3430</v>
+        <v>5209</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -601,15 +595,15 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>1620</v>
+        <v>1552.5</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>4032</v>
+        <v>6097</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -618,32 +612,32 @@
         <v>29</v>
       </c>
       <c r="D11">
-        <v>315</v>
+        <v>865</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>4223</v>
+        <v>6097</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="D12">
-        <v>734.5</v>
+        <v>432.5</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>4223</v>
+        <v>12662</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -652,15 +646,15 @@
         <v>1</v>
       </c>
       <c r="D13">
-        <v>8814</v>
+        <v>471.75</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>10124</v>
+        <v>21704</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
@@ -669,27 +663,27 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>290.75</v>
+        <v>684</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>25960</v>
+        <v>21704</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>107.25</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/manual/output_703_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_703_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,31 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>راني عصير خوخ حبيبات- 235 مل</t>
-  </si>
-  <si>
-    <t>زيت عافية ذرة - 2.2 لتر</t>
-  </si>
-  <si>
     <t>سوفى ماكسى بالمسك طويل سميكة عرض خاص - 16 فوطة</t>
   </si>
   <si>
-    <t>سبرايت - 0.95 لتر</t>
-  </si>
-  <si>
-    <t>لبان تشكلتس نعناع - 0.5 جنية</t>
-  </si>
-  <si>
-    <t>لبان تشكلتس فراولة - 0.5 جنية</t>
-  </si>
-  <si>
-    <t>حفاضات جود كير مقاس 5 - 100 حفاضة</t>
-  </si>
-  <si>
-    <t>زيت عافية ذرة - 700 مل</t>
-  </si>
-  <si>
-    <t>باندا مثلثات - 8 قطعه</t>
+    <t>مسحوق باهى يدوى لافندر 12 كيس- 135 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -422,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -450,7 +429,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>202</v>
+        <v>2912</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -459,231 +438,44 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>402.5</v>
+        <v>76.5</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>2538</v>
+        <v>2912</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>920</v>
+        <v>612</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>2912</v>
+        <v>24566</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>606</v>
+        <v>96.5</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>2912</v>
-      </c>
-      <c r="B5" t="s">
         <v>9</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>75.75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>3674</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>123.75</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>5208</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1605</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>5208</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>53.5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>5209</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>51.75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>5209</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1552.5</v>
-      </c>
-      <c r="E10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>6097</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11">
-        <v>29</v>
-      </c>
-      <c r="D11">
-        <v>865</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>6097</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12">
-        <v>80</v>
-      </c>
-      <c r="D12">
-        <v>432.5</v>
-      </c>
-      <c r="E12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>12662</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>471.75</v>
-      </c>
-      <c r="E13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21704</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>684</v>
-      </c>
-      <c r="E14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21704</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>19</v>
-      </c>
-      <c r="E15" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/manual/output_703_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_703_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="25">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,55 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>عصير سن توب جوافة - 250 مل</t>
-  </si>
-  <si>
-    <t>شويبس رمان بلاستيك - 250 مل</t>
+    <t>حبوبة خل- 900 مل</t>
+  </si>
+  <si>
+    <t>رويال أعشاب كركديه - 20 فتلة</t>
+  </si>
+  <si>
+    <t>حفاضات جود كير مقاس 5 - 100 حفاضة</t>
+  </si>
+  <si>
+    <t>ستينج فراولة مينى تربو - 250 مل</t>
+  </si>
+  <si>
+    <t>فاين بيبى حفاضات دبل لوك صغير مقاس 2 - 58 حفاضة</t>
+  </si>
+  <si>
+    <t>فاين بيبى حفاضات دبل لوك وسط مقاس 3 - 58 حفاضة</t>
+  </si>
+  <si>
+    <t>فاين بيبى حفاضات دبل لوك كبير مقاس 4 - 58 حفاضة</t>
+  </si>
+  <si>
+    <t>فاين بيبى حفاضات دبل لوك ماكس مقاس 5 - 58 حفاضة</t>
+  </si>
+  <si>
+    <t>سمنة حبوبة نباتى صفراء - 300 جم</t>
+  </si>
+  <si>
+    <t>حفاضات بيبى جوى مضغوطة جيب مانع للتسريب صغير مقاس 2 - 60 حفاضة</t>
+  </si>
+  <si>
+    <t>شويبس خوخ بلاستيك - 250 مل</t>
+  </si>
+  <si>
+    <t>المراعي جبنه رومي 500 جم</t>
+  </si>
+  <si>
+    <t>حفاضات فاين بيبى مقاس 2 دبل لوك - 84 حفاضة</t>
+  </si>
+  <si>
+    <t>حفاضات فاين بيبى مقاس 3 دبل لوك - 80 حفاضة</t>
+  </si>
+  <si>
+    <t>حفاضات فاين بيبى ماكسى مقاس 4 دبل لوك - 80 حفاضة</t>
+  </si>
+  <si>
+    <t>حفاضات فاين بيبى كبير مقاس 5 دبل لوك - 76 حفاضة</t>
+  </si>
+  <si>
+    <t>فاين برستيج عرض خاص 500 منديل  "6 شرينك" * 3 طبقة 500 منديل</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,7 +474,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>7182</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,27 +483,469 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>255</v>
+        <v>152.5</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>11685</v>
+        <v>4175</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>4175</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1296</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>6097</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>29</v>
+      </c>
+      <c r="D5">
+        <v>882.5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>6097</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>80</v>
+      </c>
+      <c r="D6">
+        <v>441.25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>6158</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="D7">
+        <v>115</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>9207</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>246.5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>9207</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>29</v>
+      </c>
+      <c r="D9">
+        <v>739.5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>9208</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>886.5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>9208</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>25</v>
+      </c>
+      <c r="D11">
+        <v>295.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>9209</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>29</v>
+      </c>
+      <c r="D12">
+        <v>886.5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>9209</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>25</v>
+      </c>
+      <c r="D13">
+        <v>295.5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>9239</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <v>340</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>9239</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>29</v>
+      </c>
+      <c r="D15">
+        <v>1020</v>
+      </c>
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>11403</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>328.75</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>11426</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <v>25</v>
+      </c>
+      <c r="D17">
+        <v>261.5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>11426</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>29</v>
+      </c>
+      <c r="D18">
+        <v>784.5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>11684</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
         <v>110</v>
       </c>
-      <c r="E3" t="s">
-        <v>9</v>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>12271</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>450</v>
+      </c>
+      <c r="E20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>13256</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21">
+        <v>29</v>
+      </c>
+      <c r="D21">
+        <v>689</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>13256</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22">
+        <v>25</v>
+      </c>
+      <c r="D22">
+        <v>344.5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>13257</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>734.5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>13257</v>
+      </c>
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>25</v>
+      </c>
+      <c r="D24">
+        <v>367.25</v>
+      </c>
+      <c r="E24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>13258</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25">
+        <v>29</v>
+      </c>
+      <c r="D25">
+        <v>737</v>
+      </c>
+      <c r="E25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>13258</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26">
+        <v>25</v>
+      </c>
+      <c r="D26">
+        <v>368.5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>13259</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27">
+        <v>29</v>
+      </c>
+      <c r="D27">
+        <v>848</v>
+      </c>
+      <c r="E27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>13259</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28">
+        <v>25</v>
+      </c>
+      <c r="D28">
+        <v>424</v>
+      </c>
+      <c r="E28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>13264</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29">
+        <v>29</v>
+      </c>
+      <c r="D29">
+        <v>407</v>
+      </c>
+      <c r="E29" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/manual/output_703_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_703_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,85 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>نوفى فينجرز أصابع البسكويت مغطاه بشيكولاتة الحليب - 5 جنية</t>
-  </si>
-  <si>
-    <t>نوفي فينجرز شيكولاتة بيضاء - 5 جنية</t>
+    <t>زيت حلوة خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 2.1 لتر</t>
+  </si>
+  <si>
+    <t>زيت هدية خليط- 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>هنادى زيت خليط- 2.1 لتر</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>هدية زيت خليط- 0.7 لتر</t>
+  </si>
+  <si>
+    <t>سلايت زيت عباد الشمس- 2.1 لتر</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 2.25 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت عافية عباد الشمس - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت صنى خليط عباد الشمس - 2.4 لتر</t>
+  </si>
+  <si>
+    <t>هنادى زيت خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 4.5 لتر</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة - 3.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت عافية عباد الشمس - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 550 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,7 +504,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21686</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,61 +513,452 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>294</v>
+        <v>610</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21686</v>
+        <v>448</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>24.5</v>
+        <v>625</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21687</v>
+        <v>470</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>288</v>
+        <v>863.5</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21687</v>
+        <v>471</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
+        <v>612.25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>479</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>878.75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>823</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>764.5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>856</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>869</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>858</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>605</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>922</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>612</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>924</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>612</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>1084</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>716</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>1091</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>655</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>1490</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>604</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>1492</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>860</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>2537</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>802</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>2608</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>725.25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>2851</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>861.25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>2879</v>
+      </c>
+      <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
-        <v>9</v>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>810</v>
+      </c>
+      <c r="E19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>2935</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>892.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>4203</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>640</v>
+      </c>
+      <c r="E21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>6497</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>855</v>
+      </c>
+      <c r="E22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>7520</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1464.75</v>
+      </c>
+      <c r="E23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>11962</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>681.75</v>
+      </c>
+      <c r="E24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>12661</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>387</v>
+      </c>
+      <c r="E25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>12923</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>855</v>
+      </c>
+      <c r="E26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>12924</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>600</v>
+      </c>
+      <c r="E27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>12925</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>490</v>
+      </c>
+      <c r="E28" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/manual/output_703_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_703_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,22 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>توشيبا احمر قلم كارت AA - 4 حجر</t>
-  </si>
-  <si>
-    <t>توشيبا احمر ريموت كارت AAA - 4 حجر</t>
-  </si>
-  <si>
-    <t>ليندو برو برائحه اللافندر - 200 جرام</t>
-  </si>
-  <si>
-    <t>ليندو برو برائحه اللافندر - 1.5 كجم</t>
-  </si>
-  <si>
-    <t>ليندو برو برائحه اللافندر  - 2 كجم</t>
-  </si>
-  <si>
-    <t>جبنة باندا رومى - 500 جم</t>
+    <t>شويبس ليمون نعناع  بلاستيك - 250 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -413,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -441,138 +426,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>12607</v>
+        <v>11683</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>370</v>
+        <v>110.5</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>12607</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1850</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>12608</v>
-      </c>
-      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>370</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>12608</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1850</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>13599</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>93</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>13604</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>284.25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>13606</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>366</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21771</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>417.5</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
